--- a/reports/播客监控日报_2026-05-14.xlsx
+++ b/reports/播客监控日报_2026-05-14.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1705008</v>
+        <v>1706164</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -555,27 +555,27 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>829883</t>
+          <t>833896</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:54</t>
+          <t>2026-05-14 14:48:11</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>768094</v>
+        <v>768772</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -620,27 +620,27 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:34</t>
+          <t>2026-05-14 14:47:51</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>626626</v>
+        <v>627398</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -685,27 +685,27 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46358</t>
+          <t>54971</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>375</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:38</t>
+          <t>2026-05-14 14:47:55</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>399979</v>
+        <v>400557</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -750,27 +750,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:40</t>
+          <t>2026-05-14 14:47:57</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>200230</v>
+        <v>200875</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -815,27 +815,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>190</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:38</t>
+          <t>2026-05-14 14:46:58</t>
         </is>
       </c>
     </row>
@@ -866,51 +866,51 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>165855</v>
+        <v>166038</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>episode 51｜ 长期护理市场失灵带来的宏观挑战与对策</t>
+          <t>episode 52｜中金机器人播客 Aibee林元庆：人形机器人需要第一视角，还是更聪明的世界</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47:45</t>
+          <t>1:23:10</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:30</t>
+          <t>2026-05-14 14:47:49</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>153111</v>
+        <v>153251</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -945,27 +945,27 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>345</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>482</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:42</t>
+          <t>2026-05-14 14:47:59</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>其他金融机构</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>150062</v>
+        <v>150655</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20395</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>125</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:26</t>
+          <t>2026-05-14 14:47:45</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>145342</v>
+        <v>145910</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>212</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:52</t>
+          <t>2026-05-14 14:48:09</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>143246</v>
+        <v>144094</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1140,27 +1140,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>170</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:36</t>
+          <t>2026-05-14 14:47:53</t>
         </is>
       </c>
     </row>
@@ -1191,51 +1191,51 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>104786</v>
+        <v>105345</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51. 硅谷调研手记丨AI能力边界、大厂收入与从业者焦虑</t>
+          <t>52.中美对话进行时！如何理解大国化工的发展生态和投资逻辑？</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58:06</t>
+          <t>55:20</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:40</t>
+          <t>2026-05-14 14:46:59</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>85147</v>
+        <v>85271</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -1270,27 +1270,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:46</t>
+          <t>2026-05-14 14:48:03</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>82229</v>
+        <v>82419</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1335,27 +1335,27 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>269</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>202</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:48</t>
+          <t>2026-05-14 14:48:05</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>其他金融机构</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>53735</v>
+        <v>53790</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:24</t>
+          <t>2026-05-14 14:47:43</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50051</v>
+        <v>50138</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:42</t>
+          <t>2026-05-14 14:47:01</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>34570</v>
+        <v>34597</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:44</t>
+          <t>2026-05-14 14:48:01</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>28252</v>
+        <v>28267</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:46</t>
+          <t>2026-05-14 14:47:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>泰度Voice</t>
+          <t>深度求真</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1642,120 +1642,120 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>华泰证券</t>
+          <t>大成基金</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22789</v>
+        <v>22892</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
+          <t>21. 世界读书日：阅读，是一个人最慢也最稳的复利</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>361</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>578</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1:00:39</t>
+          <t>1:00:26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:22</t>
+          <t>2026-05-14 14:47:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>深度求真</t>
+          <t>泰度Voice</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>其他金融机构</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>大成基金</t>
+          <t>华泰证券</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22695</v>
+        <v>22789</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21. 世界读书日：阅读，是一个人最慢也最稳的复利</t>
+          <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1:00:26</t>
+          <t>1:00:39</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:48</t>
+          <t>2026-05-14 14:47:41</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>19364</v>
+        <v>19403</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:50</t>
+          <t>2026-05-14 14:48:07</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>公募基金</t>
+          <t>其他金融机构</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>9704</v>
+        <v>9707</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:20</t>
+          <t>2026-05-14 14:47:39</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9044</v>
+        <v>9066</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>933</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:16</t>
+          <t>2026-05-14 14:47:35</t>
         </is>
       </c>
     </row>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9030</v>
+        <v>9050</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>340.5月13日财经速递</t>
+          <t>341.5月14日财经速递</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3:33</t>
+          <t>3:36</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:58</t>
+          <t>2026-05-14 14:47:17</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>8785</v>
+        <v>8878</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>156</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>276</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:08</t>
+          <t>2026-05-14 14:47:27</t>
         </is>
       </c>
     </row>
@@ -2101,51 +2101,51 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7609</v>
+        <v>7629</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15. 养虾成本狂飙？“算电协同”如何叠满“电力 + 算力”双buff</t>
+          <t>16.订单排满、盈利修复、储能变现…“周期成长”的新能源，赚钱逻辑正在何处？</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1:08:16</t>
+          <t>1:00:19</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:04</t>
+          <t>2026-05-14 14:47:23</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6821</v>
+        <v>6828</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:06</t>
+          <t>2026-05-14 14:47:25</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4592</v>
+        <v>4593</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:10</t>
+          <t>2026-05-14 14:47:29</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3916</v>
+        <v>3919</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:12</t>
+          <t>2026-05-14 14:47:31</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3320</v>
+        <v>3322</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:50</t>
+          <t>2026-05-14 14:47:09</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:14</t>
+          <t>2026-05-14 14:47:33</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:56</t>
+          <t>2026-05-14 14:47:15</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:00</t>
+          <t>2026-05-14 14:47:19</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:44</t>
+          <t>2026-05-14 14:47:03</t>
         </is>
       </c>
     </row>
@@ -2730,67 +2730,79 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:18</t>
+          <t>2026-05-14 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>对话金融人</t>
+          <t>解盘一刻</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>其他金融机构</t>
+          <t>公募基金</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>广发证券</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>477</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+        <v>427</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:32</t>
+          <t>2026-05-14 14:47:47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>解盘一刻</t>
+          <t>基金经理一周论市</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2800,25 +2812,25 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>华夏基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>427</v>
+        <v>316</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
+          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2843,19 +2855,19 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>2:01</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:01:28</t>
+          <t>2026-05-14 14:47:11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>基金经理一周论市</t>
+          <t>好朋友</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2865,25 +2877,25 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>中泰资管</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>316</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
+          <t>Vol.6 饭后闲聊，食物里的权力、爱与自我救赎</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2893,34 +2905,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2:01</t>
+          <t>1:37:31</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:52</t>
+          <t>2026-05-14 14:47:13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>好朋友</t>
+          <t>投资心法</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2930,25 +2942,25 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>国投瑞银基金</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Vol.6 饭后闲聊，食物里的权力、爱与自我救赎</t>
+          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2958,92 +2970,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1:37:31</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 23:00:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>投资心法</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>公募基金</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>国投瑞银基金</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>19:39</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13 23:01:02</t>
+          <t>2026-05-14 14:47:21</t>
         </is>
       </c>
     </row>
